--- a/usecase2_demand_forecasting/input/input_agent_roster.xlsx
+++ b/usecase2_demand_forecasting/input/input_agent_roster.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="98">
   <si>
     <t>agent_id</t>
   </si>
@@ -160,148 +160,154 @@
     <t>AGT1039</t>
   </si>
   <si>
-    <t>Kavya Joshi (1)</t>
-  </si>
-  <si>
-    <t>Ananya Joshi (2)</t>
-  </si>
-  <si>
-    <t>Kavya Pillai (3)</t>
-  </si>
-  <si>
-    <t>Meera Joshi (4)</t>
-  </si>
-  <si>
-    <t>Kabir Joshi (5)</t>
-  </si>
-  <si>
-    <t>Ananya Verma (6)</t>
-  </si>
-  <si>
-    <t>Kavya Reddy (7)</t>
-  </si>
-  <si>
-    <t>Karan Verma (8)</t>
-  </si>
-  <si>
-    <t>Aryan Pillai (9)</t>
-  </si>
-  <si>
-    <t>Neha Joshi (10)</t>
-  </si>
-  <si>
-    <t>Aditya Shetty (11)</t>
-  </si>
-  <si>
-    <t>Ishaan Shetty (12)</t>
-  </si>
-  <si>
-    <t>Aditya Shetty (13)</t>
-  </si>
-  <si>
-    <t>Karan Gupta (14)</t>
-  </si>
-  <si>
-    <t>Riya Gupta (15)</t>
-  </si>
-  <si>
-    <t>Kabir Shetty (16)</t>
-  </si>
-  <si>
-    <t>Diya Gupta (17)</t>
-  </si>
-  <si>
-    <t>Kavya Shetty (18)</t>
-  </si>
-  <si>
-    <t>Ananya Pillai (19)</t>
-  </si>
-  <si>
-    <t>Sanya Pillai (20)</t>
-  </si>
-  <si>
-    <t>Ananya Pillai (21)</t>
-  </si>
-  <si>
-    <t>Rohan Reddy (22)</t>
-  </si>
-  <si>
-    <t>Karan Verma (23)</t>
-  </si>
-  <si>
-    <t>Kabir Joshi (24)</t>
-  </si>
-  <si>
-    <t>Kabir Joshi (25)</t>
-  </si>
-  <si>
-    <t>Ananya Shetty (26)</t>
-  </si>
-  <si>
-    <t>Karan Reddy (27)</t>
-  </si>
-  <si>
-    <t>Ananya Shetty (28)</t>
-  </si>
-  <si>
-    <t>Vivaan Shetty (29)</t>
-  </si>
-  <si>
-    <t>Sanya Gupta (30)</t>
-  </si>
-  <si>
-    <t>Vivaan Khan (31)</t>
-  </si>
-  <si>
-    <t>Kavya Gupta (32)</t>
-  </si>
-  <si>
-    <t>Vivaan Verma (33)</t>
-  </si>
-  <si>
-    <t>Kabir Reddy (34)</t>
-  </si>
-  <si>
-    <t>Kabir Reddy (35)</t>
-  </si>
-  <si>
-    <t>Aditya Joshi (36)</t>
-  </si>
-  <si>
-    <t>Neha Khan (37)</t>
-  </si>
-  <si>
-    <t>Meera Pillai (38)</t>
-  </si>
-  <si>
-    <t>Riya Gupta (39)</t>
-  </si>
-  <si>
-    <t>Aryan Shetty (40)</t>
+    <t>Farhan Rana</t>
+  </si>
+  <si>
+    <t>Tanvi Iyer</t>
+  </si>
+  <si>
+    <t>Zoya Banerjee</t>
+  </si>
+  <si>
+    <t>Manish Nambiar</t>
+  </si>
+  <si>
+    <t>Simran Ghosh</t>
+  </si>
+  <si>
+    <t>Naina Yadav</t>
+  </si>
+  <si>
+    <t>Arjun Khan</t>
+  </si>
+  <si>
+    <t>Imran Saxena</t>
+  </si>
+  <si>
+    <t>Kabir Shetty</t>
+  </si>
+  <si>
+    <t>Karan Nair</t>
+  </si>
+  <si>
+    <t>Meera Rathore</t>
+  </si>
+  <si>
+    <t>Varun Mishra</t>
+  </si>
+  <si>
+    <t>Yash Agarwal</t>
+  </si>
+  <si>
+    <t>Neha Bhatt</t>
+  </si>
+  <si>
+    <t>Aarav Kulkarni</t>
+  </si>
+  <si>
+    <t>Ananya Bose</t>
+  </si>
+  <si>
+    <t>Rajat Patel</t>
+  </si>
+  <si>
+    <t>Anika Kapoor</t>
+  </si>
+  <si>
+    <t>Rohan Sinha</t>
+  </si>
+  <si>
+    <t>Nikhil Gupta</t>
+  </si>
+  <si>
+    <t>Rahul Kaur</t>
+  </si>
+  <si>
+    <t>Siddharth Reddy</t>
+  </si>
+  <si>
+    <t>Aditya Bhatia</t>
+  </si>
+  <si>
+    <t>Shreya Verma</t>
+  </si>
+  <si>
+    <t>Ritu Chopra</t>
+  </si>
+  <si>
+    <t>Pooja Pillai</t>
+  </si>
+  <si>
+    <t>Vivaan Thakur</t>
+  </si>
+  <si>
+    <t>Aman Chauhan</t>
+  </si>
+  <si>
+    <t>Ishaan Malhotra</t>
+  </si>
+  <si>
+    <t>Ishita Joshi</t>
+  </si>
+  <si>
+    <t>Sanya Dutta</t>
+  </si>
+  <si>
+    <t>Kavya Pandey</t>
+  </si>
+  <si>
+    <t>Alisha Sharma</t>
+  </si>
+  <si>
+    <t>Riya Mehta</t>
+  </si>
+  <si>
+    <t>Harsh Menon</t>
+  </si>
+  <si>
+    <t>Priyanka Srinivasan</t>
+  </si>
+  <si>
+    <t>Sneha Trivedi</t>
+  </si>
+  <si>
+    <t>Aryan Choudhury</t>
+  </si>
+  <si>
+    <t>Diya Oberoi</t>
+  </si>
+  <si>
+    <t>Dev Desai</t>
+  </si>
+  <si>
+    <t>Broadband</t>
+  </si>
+  <si>
+    <t>Prepaid Mobile</t>
   </si>
   <si>
     <t>Postpaid Mobile</t>
   </si>
   <si>
-    <t>Broadband</t>
+    <t>Billing &amp; Payments</t>
+  </si>
+  <si>
+    <t>Arjun Rao</t>
+  </si>
+  <si>
+    <t>Deepa Menon</t>
+  </si>
+  <si>
+    <t>Priya Nair</t>
   </si>
   <si>
     <t>Vikram Singh</t>
   </si>
   <si>
-    <t>Arjun Rao</t>
-  </si>
-  <si>
-    <t>Priya Nair</t>
-  </si>
-  <si>
-    <t>Deepa Menon</t>
+    <t>Anita Sharma</t>
   </si>
   <si>
     <t>Rajesh Kumar</t>
-  </si>
-  <si>
-    <t>Anita Sharma</t>
   </si>
 </sst>
 </file>
@@ -673,19 +679,19 @@
         <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>40</v>
+      </c>
+      <c r="H2">
         <v>24</v>
-      </c>
-      <c r="G2">
-        <v>40</v>
-      </c>
-      <c r="H2">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -696,22 +702,22 @@
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>40</v>
       </c>
       <c r="H3">
-        <v>14.8</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -722,22 +728,22 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F4">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>12</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -748,22 +754,22 @@
         <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="G5">
         <v>40</v>
       </c>
       <c r="H5">
-        <v>22.7</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -774,22 +780,22 @@
         <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G6">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H6">
-        <v>24</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -800,22 +806,22 @@
         <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F7">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7">
         <v>18</v>
-      </c>
-      <c r="G7">
-        <v>30</v>
-      </c>
-      <c r="H7">
-        <v>19.7</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -826,22 +832,22 @@
         <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>40</v>
       </c>
       <c r="H8">
-        <v>24.5</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -852,22 +858,22 @@
         <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
         <v>93</v>
       </c>
       <c r="E9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H9">
-        <v>18.4</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -881,19 +887,19 @@
         <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G10">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H10">
-        <v>24.3</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -904,22 +910,22 @@
         <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F11">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="G11">
         <v>40</v>
       </c>
       <c r="H11">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -930,22 +936,22 @@
         <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>40</v>
       </c>
       <c r="H12">
-        <v>26.3</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -956,22 +962,22 @@
         <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
         <v>93</v>
       </c>
       <c r="E13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13">
         <v>40</v>
       </c>
       <c r="H13">
-        <v>24.1</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -982,22 +988,22 @@
         <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="G14">
         <v>40</v>
       </c>
       <c r="H14">
-        <v>23.3</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1008,22 +1014,22 @@
         <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E15" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F15">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="G15">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H15">
-        <v>23.7</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1034,22 +1040,22 @@
         <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E16" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F16">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="G16">
         <v>40</v>
       </c>
       <c r="H16">
-        <v>22.5</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1060,22 +1066,22 @@
         <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G17">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H17">
-        <v>19.9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1086,22 +1092,22 @@
         <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F18">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G18">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H18">
-        <v>18.8</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1112,22 +1118,22 @@
         <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F19">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G19">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H19">
-        <v>24.2</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1138,22 +1144,22 @@
         <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F20">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G20">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H20">
-        <v>17.3</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1164,22 +1170,22 @@
         <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
         <v>92</v>
       </c>
       <c r="E21" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F21">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="G21">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H21">
-        <v>13.7</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1190,13 +1196,13 @@
         <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F22">
         <v>12</v>
@@ -1205,7 +1211,7 @@
         <v>40</v>
       </c>
       <c r="H22">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1216,13 +1222,13 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F23">
         <v>18</v>
@@ -1231,7 +1237,7 @@
         <v>40</v>
       </c>
       <c r="H23">
-        <v>17.7</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1242,22 +1248,22 @@
         <v>70</v>
       </c>
       <c r="C24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F24">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G24">
         <v>40</v>
       </c>
       <c r="H24">
-        <v>19.7</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1274,16 +1280,16 @@
         <v>93</v>
       </c>
       <c r="E25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F25">
         <v>18</v>
       </c>
       <c r="G25">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H25">
-        <v>19.2</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1294,22 +1300,22 @@
         <v>72</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G26">
         <v>40</v>
       </c>
       <c r="H26">
-        <v>23.8</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1320,22 +1326,22 @@
         <v>73</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
         <v>92</v>
       </c>
       <c r="E27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F27">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="G27">
         <v>40</v>
       </c>
       <c r="H27">
-        <v>16</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1346,22 +1352,22 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F28">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G28">
         <v>20</v>
       </c>
       <c r="H28">
-        <v>16.9</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1372,22 +1378,22 @@
         <v>75</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F29">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G29">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H29">
-        <v>10</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1398,22 +1404,22 @@
         <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E30" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F30">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G30">
         <v>30</v>
       </c>
       <c r="H30">
-        <v>27.5</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1424,22 +1430,22 @@
         <v>77</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D31" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E31" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F31">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G31">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H31">
-        <v>25.9</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1450,22 +1456,22 @@
         <v>78</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E32" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F32">
         <v>24</v>
       </c>
       <c r="G32">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H32">
-        <v>16</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1476,22 +1482,22 @@
         <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E33" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F33">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G33">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H33">
-        <v>21.8</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1502,22 +1508,22 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D34" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F34">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G34">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H34">
-        <v>22.1</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1531,19 +1537,19 @@
         <v>89</v>
       </c>
       <c r="D35" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E35" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F35">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G35">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H35">
-        <v>16</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1554,22 +1560,22 @@
         <v>82</v>
       </c>
       <c r="C36" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D36" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E36" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G36">
         <v>40</v>
       </c>
       <c r="H36">
-        <v>25.7</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1580,13 +1586,13 @@
         <v>83</v>
       </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D37" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E37" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F37">
         <v>18</v>
@@ -1595,7 +1601,7 @@
         <v>40</v>
       </c>
       <c r="H37">
-        <v>20.9</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1606,13 +1612,13 @@
         <v>84</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D38" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E38" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F38">
         <v>9</v>
@@ -1621,7 +1627,7 @@
         <v>40</v>
       </c>
       <c r="H38">
-        <v>25.2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1632,22 +1638,22 @@
         <v>85</v>
       </c>
       <c r="C39" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D39" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E39" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F39">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="G39">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H39">
-        <v>17.1</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1664,16 +1670,16 @@
         <v>93</v>
       </c>
       <c r="E40" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F40">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G40">
         <v>40</v>
       </c>
       <c r="H40">
-        <v>23.4</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1684,22 +1690,22 @@
         <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D41" t="s">
         <v>92</v>
       </c>
       <c r="E41" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F41">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G41">
         <v>40</v>
       </c>
       <c r="H41">
-        <v>18.6</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
